--- a/reports/devops-jobs-israel-2026-W30.xlsx
+++ b/reports/devops-jobs-israel-2026-W30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-20T09:30:32</t>
+    <t xml:space="preserve">2026-07-21T08:40:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8%</t>
+    <t xml:space="preserve">2.3%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -414,6 +414,21 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
   </si>
   <si>
@@ -426,13 +441,439 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software AG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Penlink</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-20</t>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps and Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceragon Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeerSpot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinecone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of QA Automation and DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nisha-pro-4440409970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-one-systems-4442022722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36998)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4438720709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Ground Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-ground-systems-at-airobotics-4442025007</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevSecOps Engineer</t>
@@ -441,855 +882,471 @@
     <t xml:space="preserve">Infinidat</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-infinidat-4437658931</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-15</t>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Airborne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbit Communication Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-airborne-at-orbit-communication-systems-4441796016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belocal Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4438414159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4441783259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4443312914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4442736823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroll Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4442586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudFormation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4416059820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-log-on-software-4440128123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shavit Software</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-shavit-software-4442576674</t>
   </si>
   <si>
-    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-log-on-software-4440128123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harel Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software AG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-one-systems-4442022722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps and Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceragon Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeerSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4441985184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinecone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4438720709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Ground Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-ground-systems-at-airobotics-4442025007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-abra-4441783259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Airborne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-airborne-at-orbit-communication-systems-4441796016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belocal Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4438414159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudFormation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator VMware (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-vmware-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4441455499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1302,16 +1359,22 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1463,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -1471,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1479,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -1487,7 +1550,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="10">
@@ -1495,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1559,7 +1622,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1567,7 +1630,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1586,47 +1649,47 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>143</v>
+        <v>371</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1642,39 +1705,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>218</v>
+        <v>444</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -1682,79 +1745,79 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>429</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>330</v>
+        <v>448</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>430</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>323</v>
+        <v>450</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1762,7 +1825,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -1790,13 +1853,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2">
@@ -1804,13 +1867,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>64.4</v>
+        <v>13.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1819,88 +1882,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3">
-        <v>33.7</v>
+        <v>40.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.6</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.8</v>
+        <v>18.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.3</v>
+        <v>24.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1911,9 +1974,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1984,7 +2047,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -2016,7 +2079,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -2048,7 +2111,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -2080,7 +2143,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -2112,7 +2175,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2144,7 +2207,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -2176,7 +2239,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -2208,7 +2271,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -2240,7 +2303,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -2272,7 +2335,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -2304,7 +2367,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -2336,7 +2399,7 @@
         <v>89</v>
       </c>
       <c r="J13" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -2368,7 +2431,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2400,7 +2463,7 @@
         <v>76</v>
       </c>
       <c r="J15" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -2432,7 +2495,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -2464,7 +2527,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -2496,7 +2559,7 @@
         <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2528,7 +2591,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -2560,7 +2623,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2655,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -2622,7 +2685,7 @@
         <v>127</v>
       </c>
       <c r="J22" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -2654,7 +2717,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
@@ -2665,17 +2728,15 @@
         <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
@@ -2683,102 +2744,102 @@
         <v>134</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="J26" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2786,13 +2847,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>45</v>
@@ -2802,10 +2863,10 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J28" s="3">
         <v>5</v>
@@ -2813,19 +2874,19 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
@@ -2835,21 +2896,21 @@
         <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>44</v>
@@ -2862,13 +2923,13 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2876,13 +2937,13 @@
         <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -2892,13 +2953,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J31" s="3">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2909,7 +2970,7 @@
         <v>161</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>44</v>
@@ -2925,21 +2986,21 @@
         <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="J32" s="3">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>115</v>
@@ -2952,24 +3013,24 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>44</v>
@@ -2982,13 +3043,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -2996,10 +3057,10 @@
         <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>155</v>
+        <v>56</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>44</v>
@@ -3012,40 +3073,40 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
@@ -3053,46 +3114,46 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="J37" s="3">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>45</v>
@@ -3102,13 +3163,13 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3116,13 +3177,13 @@
         <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>45</v>
@@ -3132,27 +3193,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>187</v>
+        <v>56</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>45</v>
@@ -3162,24 +3223,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="J40" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
@@ -3187,29 +3248,31 @@
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J41" s="3">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>115</v>
@@ -3217,18 +3280,20 @@
       <c r="E42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3239,10 +3304,10 @@
         <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>38</v>
@@ -3252,54 +3317,54 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -3312,27 +3377,27 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="J45" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>45</v>
@@ -3342,24 +3407,24 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
@@ -3372,88 +3437,84 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>44</v>
+        <v>217</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="J48" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>218</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>115</v>
@@ -3466,27 +3527,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>45</v>
@@ -3496,70 +3557,70 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>233</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>45</v>
+        <v>233</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
@@ -3567,43 +3628,43 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
@@ -3616,24 +3677,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="J55" s="3">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
@@ -3646,40 +3707,40 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J56" s="3">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="J57" s="3">
         <v>1</v>
@@ -3687,46 +3748,46 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="J58" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>45</v>
@@ -3736,27 +3797,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>45</v>
@@ -3766,87 +3827,87 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>142</v>
+        <v>238</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="J61" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>263</v>
+        <v>124</v>
       </c>
       <c r="J62" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>45</v>
@@ -3856,24 +3917,24 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>115</v>
@@ -3882,60 +3943,62 @@
         <v>38</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>149</v>
+        <v>274</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>124</v>
+        <v>238</v>
       </c>
       <c r="J65" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>44</v>
@@ -3944,33 +4007,33 @@
         <v>45</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>83</v>
       </c>
       <c r="J66" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>279</v>
+        <v>151</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>45</v>
@@ -3980,27 +4043,27 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I67" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>109</v>
+        <v>282</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>45</v>
@@ -4010,13 +4073,13 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>284</v>
+        <v>156</v>
       </c>
       <c r="J68" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4027,15 +4090,17 @@
         <v>286</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>227</v>
+        <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
@@ -4043,27 +4108,27 @@
         <v>287</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
@@ -4073,7 +4138,7 @@
         <v>289</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4087,10 +4152,10 @@
         <v>291</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>44</v>
+        <v>217</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>45</v>
@@ -4103,24 +4168,24 @@
         <v>292</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>293</v>
+        <v>156</v>
       </c>
       <c r="J71" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>297</v>
+        <v>115</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>45</v>
@@ -4130,24 +4195,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>115</v>
@@ -4160,27 +4225,27 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>45</v>
@@ -4190,27 +4255,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>45</v>
@@ -4220,24 +4285,24 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>115</v>
@@ -4250,24 +4315,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>115</v>
@@ -4280,24 +4345,24 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>315</v>
+        <v>157</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>115</v>
@@ -4310,47 +4375,349 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="J78" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="I80" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="3" t="s">
+      <c r="C81" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J84" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J79" s="3">
-        <v>46</v>
+      <c r="E85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J85" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J88" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
+  <autoFilter ref="A1:J89"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4430,6 +4797,16 @@
     <hyperlink ref="H77" r:id="rId76"/>
     <hyperlink ref="H78" r:id="rId77"/>
     <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4437,9 +4814,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4471,13 +4848,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4485,18 +4862,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4504,18 +4881,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4523,7 +4900,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -4531,10 +4908,10 @@
         <v>109</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>145</v>
+        <v>260</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4542,18 +4919,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>194</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4561,7 +4938,7 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>196</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
@@ -4569,10 +4946,10 @@
         <v>109</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4580,18 +4957,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4599,18 +4976,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>234</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>182</v>
+        <v>316</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4618,18 +4995,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4637,18 +5014,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>181</v>
+        <v>335</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4656,18 +5033,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>296</v>
+        <v>158</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -4675,49 +5052,11 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4730,8 +5069,6 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4745,23 +5082,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B3" s="3">
         <v>14</v>
@@ -4769,7 +5106,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3">
         <v>13</v>
@@ -4777,7 +5114,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="B5" s="3">
         <v>12</v>
@@ -4785,7 +5122,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -4793,15 +5130,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -4809,7 +5146,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -4817,7 +5154,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -4825,7 +5162,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -4833,7 +5170,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4841,7 +5178,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4849,7 +5186,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -4857,7 +5194,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -4865,7 +5202,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -4887,7 +5224,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -4948,7 +5285,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4956,7 +5293,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -4964,7 +5301,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -4972,15 +5309,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>294</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -4988,7 +5325,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -4996,7 +5333,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5004,7 +5341,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5025,16 +5362,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -5154,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="3">
         <v>2.8</v>
@@ -5168,7 +5505,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="C11" s="3">
         <v>2.8</v>
@@ -5182,7 +5519,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C12" s="3">
         <v>2.6</v>
@@ -5196,13 +5533,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>294</v>
       </c>
       <c r="C13" s="3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5210,10 +5547,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3">
-        <v>2.0</v>
+        <v>2.3</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -5224,10 +5561,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3">
-        <v>1.4</v>
+        <v>2.0</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -5238,10 +5575,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -5264,18 +5601,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5286,10 +5623,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
@@ -5297,10 +5634,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -5319,7 +5656,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
@@ -5327,7 +5664,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -5335,12 +5672,12 @@
         <v>115</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5348,7 +5685,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -5356,7 +5693,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5364,15 +5701,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5380,7 +5717,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5395,7 +5732,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5407,10 +5744,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5422,10 +5759,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5442,31 +5779,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -5474,31 +5811,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>317</v>
+        <v>231</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
@@ -5506,31 +5843,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
@@ -5538,31 +5875,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>158</v>
+        <v>380</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="F5" s="3">
         <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>253</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6">
@@ -5570,31 +5907,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="F6" s="3">
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -5602,31 +5939,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>149</v>
+        <v>388</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="F7" s="3">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>168</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8">
@@ -5634,31 +5971,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
@@ -5666,31 +6003,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="F9" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -5698,31 +6035,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="F10" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>202</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -5730,31 +6067,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>381</v>
+        <v>235</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>382</v>
+        <v>236</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>384</v>
+        <v>237</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -5762,28 +6099,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>120</v>
+        <v>407</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>83</v>
@@ -5794,31 +6131,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>155</v>
+        <v>412</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14">
@@ -5826,31 +6163,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>416</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>417</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>260</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>61</v>
+        <v>419</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
@@ -5858,31 +6195,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>226</v>
+        <v>154</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>397</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -5890,31 +6227,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>399</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>400</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>403</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -5922,31 +6259,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18">
@@ -5954,31 +6291,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>155</v>
+        <v>388</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>411</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -5986,31 +6323,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>353</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>412</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>304</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>414</v>
+        <v>61</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -6018,31 +6355,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>418</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21">
@@ -6050,31 +6387,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>293</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W30.xlsx
+++ b/reports/devops-jobs-israel-2026-W30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-21T08:40:59</t>
+    <t xml:space="preserve">2026-07-22T08:40:21</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3%</t>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -339,7 +339,7 @@
     <t xml:space="preserve">Data Engineer - Billing Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
+    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
   </si>
   <si>
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
@@ -441,15 +441,90 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Infinity Solutions R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
+  </si>
+  <si>
     <t xml:space="preserve">CommBox</t>
   </si>
   <si>
@@ -468,805 +543,751 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
   </si>
   <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Thales</t>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4443763045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps and Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceragon Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4441985184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinecone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of QA Automation and DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37034-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442591926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4440223220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36998)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Rehovot, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps and Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceragon Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeerSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinecone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of QA Automation and DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-team-lead-at-nova-ltd-4403079881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442765779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroll Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4442586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudFormation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
   </si>
   <si>
     <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
+    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nisha-pro-4440409970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-one-systems-4442022722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4438720709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Ground Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-ground-systems-at-airobotics-4442025007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-infinidat-4437658931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Airborne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orbit Communication Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-airborne-at-orbit-communication-systems-4441796016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belocal Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4438414159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4441783259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4443312914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4442736823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kroll Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4442586353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudFormation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
@@ -1278,7 +1299,7 @@
     <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4416059820</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
   </si>
   <si>
     <t xml:space="preserve">Log-On Software</t>
@@ -1311,30 +1332,9 @@
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-shavit-software-4442576674</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
   </si>
   <si>
@@ -1356,25 +1356,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1534,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1542,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1550,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1042</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="10">
@@ -1558,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1649,28 +1646,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1678,15 +1675,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1705,7 +1702,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>442</v>
@@ -1713,15 +1710,15 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>443</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>347</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3">
         <v>38</v>
@@ -1732,31 +1729,31 @@
         <v>444</v>
       </c>
       <c r="B4" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>445</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>446</v>
+        <v>347</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1769,10 +1766,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1780,7 +1777,7 @@
         <v>448</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1788,15 +1785,15 @@
         <v>449</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1804,20 +1801,20 @@
         <v>450</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1825,10 +1822,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>451</v>
+        <v>346</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1853,13 +1850,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="2">
@@ -1870,10 +1867,10 @@
         <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1882,88 +1879,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
-        <v>40.0</v>
+        <v>33.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.7</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.9</v>
+        <v>41.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>24.7</v>
+        <v>23.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1975,8 +1972,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2047,7 +2044,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -2079,7 +2076,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -2111,7 +2108,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -2143,7 +2140,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -2175,7 +2172,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -2207,7 +2204,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -2239,7 +2236,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -2271,7 +2268,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -2303,7 +2300,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -2335,7 +2332,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -2367,7 +2364,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -2399,7 +2396,7 @@
         <v>89</v>
       </c>
       <c r="J13" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -2431,7 +2428,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2463,7 +2460,7 @@
         <v>76</v>
       </c>
       <c r="J15" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -2495,7 +2492,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -2527,7 +2524,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -2559,7 +2556,7 @@
         <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -2591,7 +2588,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -2623,7 +2620,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -2655,7 +2652,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -2685,7 +2682,7 @@
         <v>127</v>
       </c>
       <c r="J22" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -2717,7 +2714,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
@@ -2747,7 +2744,7 @@
         <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -2779,7 +2776,7 @@
         <v>76</v>
       </c>
       <c r="J25" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2806,10 +2803,10 @@
         <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2817,13 +2814,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>45</v>
@@ -2833,13 +2830,13 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2847,13 +2844,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>45</v>
@@ -2866,15 +2863,15 @@
         <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>150</v>
@@ -2896,10 +2893,10 @@
         <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="J29" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2910,10 +2907,10 @@
         <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2923,13 +2920,13 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2937,13 +2934,13 @@
         <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -2953,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2967,10 +2964,10 @@
         <v>109</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>44</v>
@@ -2983,24 +2980,24 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="J32" s="3">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>115</v>
@@ -3013,27 +3010,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J33" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>45</v>
@@ -3043,13 +3040,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="J34" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3057,7 +3054,7 @@
         <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>56</v>
@@ -3073,84 +3070,84 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>115</v>
@@ -3163,27 +3160,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>45</v>
@@ -3193,178 +3190,176 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="J39" s="3">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="J41" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -3377,13 +3372,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3394,40 +3389,42 @@
         <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="J46" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>44</v>
+        <v>215</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>45</v>
@@ -3437,87 +3434,87 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="J47" s="3">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>217</v>
+        <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="J49" s="3">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>223</v>
+        <v>156</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3530,24 +3527,24 @@
         <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>225</v>
+        <v>143</v>
       </c>
       <c r="J50" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>229</v>
+        <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>45</v>
@@ -3557,84 +3554,84 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="J52" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>44</v>
@@ -3647,24 +3644,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
@@ -3677,57 +3674,57 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>247</v>
+        <v>143</v>
       </c>
       <c r="J56" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>45</v>
@@ -3737,117 +3734,117 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>45</v>
+        <v>254</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>261</v>
+        <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>45</v>
@@ -3857,10 +3854,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>238</v>
+        <v>143</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3868,43 +3865,43 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J62" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>44</v>
@@ -3917,88 +3914,84 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>254</v>
+        <v>161</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>270</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>272</v>
+        <v>49</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>44</v>
@@ -4006,64 +3999,62 @@
       <c r="E66" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="J66" s="3">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="J67" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>45</v>
@@ -4073,72 +4064,70 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>188</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>238</v>
+        <v>143</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4146,16 +4135,16 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>226</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>217</v>
+        <v>44</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>45</v>
@@ -4165,24 +4154,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>274</v>
+        <v>161</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>115</v>
@@ -4195,27 +4184,27 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>298</v>
+        <v>56</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>45</v>
@@ -4225,57 +4214,59 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D75" s="3" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>45</v>
@@ -4285,24 +4276,24 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>306</v>
+        <v>151</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>115</v>
@@ -4315,24 +4306,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>115</v>
@@ -4345,54 +4336,54 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>190</v>
+        <v>302</v>
       </c>
       <c r="J77" s="3">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>158</v>
+        <v>305</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>158</v>
+        <v>308</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>115</v>
@@ -4400,181 +4391,181 @@
       <c r="E79" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>319</v>
+        <v>151</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="D84" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>44</v>
@@ -4587,13 +4578,13 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J85" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
@@ -4601,10 +4592,10 @@
         <v>109</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>44</v>
@@ -4617,24 +4608,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>44</v>
@@ -4647,24 +4638,24 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>44</v>
@@ -4677,24 +4668,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>115</v>
@@ -4707,13 +4698,13 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4848,13 +4839,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4862,7 +4853,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>237</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -4870,10 +4861,10 @@
         <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>239</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4881,18 +4872,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4900,7 +4891,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>258</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
@@ -4908,10 +4899,10 @@
         <v>109</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4919,18 +4910,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4938,7 +4929,7 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>275</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -4946,10 +4937,10 @@
         <v>109</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>288</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4957,18 +4948,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>289</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>312</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4976,18 +4967,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>314</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>316</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4995,18 +4986,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>332</v>
+        <v>226</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5014,18 +5005,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>240</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>335</v>
+        <v>241</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5033,18 +5024,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>336</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>175</v>
+        <v>256</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5052,11 +5043,163 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>341</v>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G20"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5069,6 +5212,14 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5082,23 +5233,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>188</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B3" s="3">
         <v>14</v>
@@ -5106,7 +5257,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B4" s="3">
         <v>13</v>
@@ -5114,7 +5265,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B5" s="3">
         <v>12</v>
@@ -5122,7 +5273,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5130,15 +5281,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -5146,7 +5297,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5154,7 +5305,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -5162,7 +5313,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5170,7 +5321,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5186,7 +5337,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5194,7 +5345,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5202,7 +5353,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -5215,7 +5366,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5224,7 +5375,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
@@ -5285,7 +5436,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5293,7 +5444,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5301,7 +5452,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5309,7 +5460,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5317,23 +5468,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>35</v>
+        <v>290</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5341,7 +5492,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5355,23 +5506,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
@@ -5424,7 +5575,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="3">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -5491,10 +5642,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5505,10 +5656,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5519,10 +5670,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -5533,7 +5684,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5547,13 +5698,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="C14" s="3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5561,13 +5712,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>297</v>
       </c>
       <c r="C15" s="3">
-        <v>2.0</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5575,10 +5726,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -5601,18 +5752,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5623,10 +5774,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4">
@@ -5634,10 +5785,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5656,7 +5807,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -5664,7 +5815,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -5672,12 +5823,12 @@
         <v>115</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5701,7 +5852,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5709,15 +5860,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5744,10 +5895,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5759,10 +5910,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5779,31 +5930,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -5811,31 +5962,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -5843,31 +5994,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
@@ -5875,31 +6026,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F5" s="3">
         <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>331</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6">
@@ -5910,28 +6061,28 @@
         <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>318</v>
+        <v>380</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -5945,25 +6096,25 @@
         <v>387</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="F7" s="3">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>391</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>392</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
@@ -5971,31 +6122,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F8" s="3">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F8" s="3">
-        <v>74</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -6003,31 +6154,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F9" s="3">
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>163</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6035,28 +6186,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F10" s="3">
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>89</v>
@@ -6067,31 +6218,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>235</v>
+        <v>400</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F11" s="3">
         <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>237</v>
+        <v>402</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
@@ -6099,28 +6250,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F12" s="3">
         <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>83</v>
@@ -6131,31 +6282,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F13" s="3">
         <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14">
@@ -6163,31 +6314,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>156</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15">
@@ -6195,31 +6346,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>367</v>
+        <v>418</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F15" s="3">
+        <v>52</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="F15" s="3">
-        <v>50</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -6227,31 +6378,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>424</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17">
@@ -6259,31 +6410,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>425</v>
+        <v>364</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>429</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
@@ -6291,28 +6442,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>430</v>
+        <v>386</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>431</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="F18" s="3">
         <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>83</v>
@@ -6323,31 +6474,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>59</v>
+        <v>432</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>433</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>434</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>61</v>
+        <v>435</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20">
@@ -6355,31 +6506,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>367</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>435</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>156</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -6396,13 +6547,13 @@
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F21" s="3">
         <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>

--- a/reports/devops-jobs-israel-2026-W30.xlsx
+++ b/reports/devops-jobs-israel-2026-W30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22T08:40:21</t>
+    <t xml:space="preserve">2026-07-23T08:42:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">2.4%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -441,777 +441,765 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4443441584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36998)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-at-commit-4440117720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of QA Automation and DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37034-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442591926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4443042028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-above-security-4443903986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infinity Solutions R2</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer - Infrastructure Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-infrastructure-team-at-mastercard-4440182633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Yona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-air-4443789369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireless Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/wireless-communication-system-engineer-at-iai-israel-aerospace-industries-4443753276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4439198034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudFormation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Software AG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4443763045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps and Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceragon Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4441985184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinecone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of QA Automation and DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37034)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37034-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442591926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedded Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4440223220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-team-lead-at-nova-ltd-4403079881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442765779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kroll Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4442586353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudFormation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -1221,13 +1209,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
@@ -1239,48 +1227,15 @@
     <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1290,25 +1245,19 @@
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-log-on-software-4440128123</t>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1317,34 +1266,70 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1353,25 +1338,28 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1523,7 +1511,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1531,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1539,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1547,7 +1535,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1061</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="10">
@@ -1555,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1619,7 +1607,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1646,47 +1634,47 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1702,63 +1690,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -1766,55 +1754,55 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>443</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>449</v>
+        <v>335</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>201</v>
+        <v>444</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>450</v>
+        <v>332</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>340</v>
+        <v>445</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1822,10 +1810,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>346</v>
+        <v>446</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1850,13 +1838,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
@@ -1867,10 +1855,10 @@
         <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1879,19 +1867,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>33.9</v>
+        <v>36.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -1900,67 +1888,67 @@
         <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.2</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>41.0</v>
+        <v>45.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.7</v>
+        <v>21.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>23.5</v>
+        <v>15.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1971,9 +1959,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2044,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -2076,7 +2064,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -2108,7 +2096,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -2140,7 +2128,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -2172,7 +2160,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -2204,7 +2192,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -2236,7 +2224,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -2268,7 +2256,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -2300,7 +2288,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -2332,7 +2320,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -2364,7 +2352,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -2396,7 +2384,7 @@
         <v>89</v>
       </c>
       <c r="J13" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -2428,7 +2416,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2460,7 +2448,7 @@
         <v>76</v>
       </c>
       <c r="J15" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -2492,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -2524,7 +2512,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -2556,7 +2544,7 @@
         <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -2588,7 +2576,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -2620,7 +2608,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -2652,7 +2640,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -2682,7 +2670,7 @@
         <v>127</v>
       </c>
       <c r="J22" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -2714,7 +2702,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2744,7 +2732,7 @@
         <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
@@ -2776,7 +2764,7 @@
         <v>76</v>
       </c>
       <c r="J25" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -2790,7 +2778,7 @@
         <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>45</v>
@@ -2806,7 +2794,7 @@
         <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2817,7 +2805,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
@@ -2830,13 +2818,13 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2844,10 +2832,10 @@
         <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2863,10 +2851,10 @@
         <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2874,13 +2862,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2890,13 +2878,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2907,10 +2895,10 @@
         <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2920,27 +2908,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -2950,27 +2938,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>45</v>
@@ -2980,27 +2968,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3010,13 +2998,13 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
@@ -3024,13 +3012,13 @@
         <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>45</v>
@@ -3040,13 +3028,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -3054,13 +3042,13 @@
         <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>45</v>
@@ -3070,13 +3058,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3084,13 +3072,13 @@
         <v>109</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>45</v>
@@ -3100,27 +3088,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>45</v>
@@ -3130,24 +3118,24 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>115</v>
@@ -3160,27 +3148,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="J38" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>45</v>
@@ -3190,54 +3178,56 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="J39" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>115</v>
@@ -3250,72 +3240,70 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>201</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3326,10 +3314,10 @@
         <v>109</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
@@ -3342,13 +3330,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="J44" s="3">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3356,10 +3344,10 @@
         <v>109</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -3372,45 +3360,43 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -3418,13 +3404,13 @@
         <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>45</v>
@@ -3434,54 +3420,54 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
@@ -3494,27 +3480,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3524,24 +3510,24 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>44</v>
@@ -3554,24 +3540,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
@@ -3584,57 +3570,57 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>45</v>
@@ -3644,207 +3630,207 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="J54" s="3">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="J55" s="3">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="J58" s="3">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="J59" s="3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>254</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="J60" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>45</v>
@@ -3854,24 +3840,24 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>143</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>109</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>115</v>
@@ -3890,7 +3876,7 @@
         <v>143</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3898,13 +3884,13 @@
         <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>45</v>
@@ -3914,54 +3900,54 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>109</v>
+        <v>264</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>49</v>
+        <v>255</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>44</v>
@@ -3974,87 +3960,89 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>109</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>45</v>
@@ -4064,10 +4052,10 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="J68" s="3">
         <v>0</v>
@@ -4075,73 +4063,73 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>109</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>109</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>44</v>
@@ -4154,27 +4142,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J71" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>45</v>
@@ -4184,21 +4172,21 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>56</v>
@@ -4214,59 +4202,57 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>62</v>
       </c>
       <c r="J73" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>289</v>
+        <v>109</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="I74" s="3" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>294</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>45</v>
@@ -4279,10 +4265,10 @@
         <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="J75" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4290,13 +4276,13 @@
         <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D76" s="3" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>45</v>
@@ -4309,10 +4295,10 @@
         <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77">
@@ -4320,10 +4306,10 @@
         <v>299</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>115</v>
@@ -4336,13 +4322,13 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>302</v>
+        <v>152</v>
       </c>
       <c r="J77" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4353,31 +4339,31 @@
         <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>305</v>
+        <v>217</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>307</v>
@@ -4389,7 +4375,7 @@
         <v>115</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4399,10 +4385,10 @@
         <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4410,26 +4396,26 @@
         <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="J80" s="3">
         <v>0</v>
@@ -4437,16 +4423,16 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4456,54 +4442,56 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>207</v>
+        <v>315</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>308</v>
+        <v>150</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>44</v>
@@ -4516,10 +4504,10 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4527,45 +4515,43 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>109</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>291</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>44</v>
@@ -4578,137 +4564,47 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J85" s="3">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J87" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J88" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J89" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J86"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4795,9 +4691,6 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
-    <hyperlink ref="H87" r:id="rId86"/>
-    <hyperlink ref="H88" r:id="rId87"/>
-    <hyperlink ref="H89" r:id="rId88"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4805,8 +4698,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4839,13 +4732,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4853,18 +4746,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4872,18 +4765,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4891,18 +4784,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>270</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>271</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4910,18 +4803,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>154</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4929,18 +4822,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>157</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>164</v>
+        <v>279</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4948,18 +4841,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4967,18 +4860,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4986,18 +4879,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>224</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5005,18 +4898,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>240</v>
+        <v>306</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>241</v>
+        <v>307</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>308</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5024,18 +4917,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>301</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5043,18 +4936,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>258</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5062,144 +4955,11 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B19" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>324</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5213,13 +4973,6 @@
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5233,23 +4986,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3">
         <v>14</v>
@@ -5257,7 +5010,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3">
         <v>13</v>
@@ -5265,7 +5018,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3">
         <v>12</v>
@@ -5273,15 +5026,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5289,7 +5042,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -5297,15 +5050,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>338</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -5313,7 +5066,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5321,7 +5074,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5337,7 +5090,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5345,7 +5098,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5353,7 +5106,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -5366,7 +5119,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5375,7 +5128,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2">
@@ -5436,7 +5189,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5444,7 +5197,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5452,7 +5205,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5460,7 +5213,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5468,7 +5221,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5476,7 +5229,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5506,23 +5259,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2">
@@ -5642,7 +5395,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C10" s="3">
         <v>2.6</v>
@@ -5656,7 +5409,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="C11" s="3">
         <v>2.4</v>
@@ -5670,7 +5423,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
@@ -5684,7 +5437,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5698,7 +5451,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5712,7 +5465,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5752,18 +5505,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5774,10 +5527,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
@@ -5785,10 +5538,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5807,7 +5560,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
@@ -5815,7 +5568,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -5823,7 +5576,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -5831,28 +5584,28 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5860,7 +5613,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5868,7 +5621,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>215</v>
+        <v>133</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5895,10 +5648,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5910,10 +5663,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5930,31 +5683,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3">
@@ -5962,31 +5715,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -5994,31 +5747,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
@@ -6026,31 +5779,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>304</v>
+        <v>153</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="3">
+        <v>81</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F5" s="3">
-        <v>76</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -6058,31 +5811,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>381</v>
+        <v>301</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>385</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
@@ -6090,31 +5843,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>156</v>
+        <v>378</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>170</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8">
@@ -6122,31 +5875,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>198</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6154,31 +5907,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F9" s="3">
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>302</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -6186,28 +5939,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="F10" s="3">
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>89</v>
@@ -6218,31 +5971,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>265</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F11" s="3">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
@@ -6250,31 +6003,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F12" s="3">
         <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13">
@@ -6282,31 +6035,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F13" s="3">
+        <v>52</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="F13" s="3">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="14">
@@ -6314,31 +6067,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15">
@@ -6346,31 +6099,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>419</v>
+        <v>121</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -6378,31 +6131,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>423</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>424</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>426</v>
+        <v>61</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -6410,31 +6163,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F17" s="3">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
@@ -6442,31 +6195,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>386</v>
+        <v>419</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>83</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19">
@@ -6474,31 +6227,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20">
@@ -6506,31 +6259,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>382</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>429</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>61</v>
+        <v>431</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -6538,31 +6291,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>217</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W30.xlsx
+++ b/reports/devops-jobs-israel-2026-W30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-23T08:42:03</t>
+    <t xml:space="preserve">2026-07-24T08:38:01</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4%</t>
+    <t xml:space="preserve">2.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -183,1081 +183,1060 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-at-commit-4440117720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of QA Automation and DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinity Solutions R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Automic Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-automic-platform-at-youcc-technologies-ltd-4441528264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4443441584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4443354508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-above-security-4443903986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QHR- ACCURATE HR SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-qhr-accurate-hr-services-4441512612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/navigation-system-engineer-at-iai-israel-aerospace-industries-4440139211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442705199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-at-commit-4440117720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudFormation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of QA Automation and DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37034)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37034-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442591926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4443827049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4442985724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-cato-networks-4421931930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon Web Services (AWS)</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4443042028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-above-security-4443903986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinity Solutions R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer - Infrastructure Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-infrastructure-team-at-mastercard-4440182633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Yona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-air-4443789369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wireless Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/wireless-communication-system-engineer-at-iai-israel-aerospace-industries-4443753276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4439198034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438781397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-platform-engineer-at-linx-security-4442764734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudFormation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MER Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1266,70 +1245,19 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1338,25 +1266,22 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1511,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -1519,7 +1444,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1527,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1535,7 +1460,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1073</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="10">
@@ -1607,7 +1532,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
@@ -1615,7 +1540,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1634,36 +1559,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1671,7 +1596,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1690,130 +1615,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>414</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>438</v>
+        <v>311</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>443</v>
+        <v>315</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>335</v>
+        <v>420</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>444</v>
+        <v>308</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>446</v>
+        <v>312</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1838,13 +1763,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
@@ -1852,13 +1777,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1867,88 +1792,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>3.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>45.3</v>
+        <v>34.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.2</v>
+        <v>16.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.1</v>
+        <v>16.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2032,7 +1957,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -2064,7 +1989,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -2096,7 +2021,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -2128,7 +2053,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -2157,21 +2082,21 @@
         <v>58</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J6" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>44</v>
@@ -2180,59 +2105,59 @@
         <v>45</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="J8" s="3">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>44</v>
@@ -2244,27 +2169,27 @@
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>44</v>
@@ -2276,19 +2201,19 @@
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J10" s="3">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -2296,7 +2221,7 @@
         <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -2317,21 +2242,21 @@
         <v>79</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>44</v>
@@ -2340,30 +2265,30 @@
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J12" s="3">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>44</v>
@@ -2372,30 +2297,30 @@
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>44</v>
@@ -2404,30 +2329,30 @@
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="J14" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>44</v>
@@ -2436,68 +2361,68 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J15" s="3">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>103</v>
@@ -2509,127 +2434,125 @@
         <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>122</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
@@ -2640,7 +2563,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
@@ -2648,29 +2571,31 @@
         <v>125</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -2678,107 +2603,105 @@
         <v>128</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="J23" s="3">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="J24" s="3">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>45</v>
@@ -2788,24 +2711,24 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
@@ -2821,15 +2744,15 @@
         <v>145</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>146</v>
@@ -2851,24 +2774,24 @@
         <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2878,27 +2801,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J29" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2908,27 +2831,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -2938,27 +2861,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>45</v>
@@ -2971,21 +2894,21 @@
         <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="J32" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>44</v>
@@ -2998,24 +2921,24 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J33" s="3">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>44</v>
@@ -3028,40 +2951,40 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="J35" s="3">
         <v>1</v>
@@ -3069,29 +2992,29 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="J36" s="3">
         <v>2</v>
@@ -3099,16 +3022,16 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>45</v>
@@ -3118,27 +3041,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>45</v>
@@ -3148,24 +3071,24 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
@@ -3178,24 +3101,24 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>44</v>
@@ -3203,94 +3126,92 @@
       <c r="E40" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="J40" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>38</v>
@@ -3300,10 +3221,10 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3311,59 +3232,59 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="J45" s="3">
         <v>66</v>
@@ -3371,16 +3292,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>45</v>
@@ -3396,21 +3317,21 @@
         <v>215</v>
       </c>
       <c r="J46" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>45</v>
@@ -3423,10 +3344,10 @@
         <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3437,13 +3358,13 @@
         <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3453,21 +3374,21 @@
         <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="J48" s="3">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
@@ -3483,7 +3404,7 @@
         <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="J49" s="3">
         <v>1</v>
@@ -3491,43 +3412,43 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>44</v>
@@ -3540,87 +3461,87 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>233</v>
+        <v>106</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="J53" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>239</v>
+        <v>106</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>45</v>
@@ -3630,57 +3551,57 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="J55" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>45</v>
@@ -3690,21 +3611,21 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>147</v>
@@ -3713,17 +3634,17 @@
         <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="J57" s="3">
         <v>1</v>
@@ -3731,16 +3652,16 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>45</v>
@@ -3753,10 +3674,10 @@
         <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="J58" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3767,10 +3688,10 @@
         <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>45</v>
@@ -3783,24 +3704,24 @@
         <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>152</v>
+        <v>255</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3810,27 +3731,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>191</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>45</v>
@@ -3840,27 +3761,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>45</v>
@@ -3870,40 +3791,40 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="J63" s="3">
         <v>1</v>
@@ -3911,10 +3832,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>264</v>
+        <v>106</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>56</v>
@@ -3923,7 +3844,7 @@
         <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -3933,91 +3854,89 @@
         <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="J64" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>44</v>
+        <v>243</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>273</v>
+        <v>49</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
@@ -4025,84 +3944,84 @@
         <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="C68" s="3" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>49</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>109</v>
+        <v>282</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>115</v>
+        <v>243</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>45</v>
@@ -4112,27 +4031,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>45</v>
@@ -4142,10 +4061,10 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4153,16 +4072,16 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>45</v>
@@ -4172,27 +4091,27 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>45</v>
@@ -4202,27 +4121,27 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="J73" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>56</v>
+        <v>295</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>45</v>
@@ -4232,379 +4151,81 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>158</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="J76" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J77" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J81" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J84" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="J85" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J86" s="3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J76"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4681,16 +4302,6 @@
     <hyperlink ref="H74" r:id="rId73"/>
     <hyperlink ref="H75" r:id="rId74"/>
     <hyperlink ref="H76" r:id="rId75"/>
-    <hyperlink ref="H77" r:id="rId76"/>
-    <hyperlink ref="H78" r:id="rId77"/>
-    <hyperlink ref="H79" r:id="rId78"/>
-    <hyperlink ref="H80" r:id="rId79"/>
-    <hyperlink ref="H81" r:id="rId80"/>
-    <hyperlink ref="H82" r:id="rId81"/>
-    <hyperlink ref="H83" r:id="rId82"/>
-    <hyperlink ref="H84" r:id="rId83"/>
-    <hyperlink ref="H85" r:id="rId84"/>
-    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4698,9 +4309,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4732,13 +4343,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4746,18 +4357,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4765,18 +4376,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4784,18 +4395,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>270</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4803,18 +4414,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4822,18 +4433,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4841,18 +4452,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4860,18 +4471,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4879,87 +4490,11 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4969,10 +4504,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4986,39 +4517,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>195</v>
+        <v>299</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="B5" s="3">
         <v>12</v>
@@ -5026,31 +4557,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="B6" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="B9" s="3">
         <v>7</v>
@@ -5058,7 +4589,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -5066,7 +4597,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5074,23 +4605,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5098,7 +4629,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5106,7 +4637,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -5119,7 +4650,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5128,12 +4659,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5149,7 +4680,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5157,15 +4688,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5173,7 +4704,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5181,7 +4712,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5189,7 +4720,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5197,7 +4728,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5205,7 +4736,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5213,31 +4744,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>274</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>300</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5245,7 +4776,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5259,23 +4790,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -5297,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3">
         <v>10.6</v>
@@ -5311,7 +4842,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3">
         <v>8.8</v>
@@ -5325,7 +4856,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3">
         <v>6.2</v>
@@ -5339,7 +4870,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3">
         <v>5.3</v>
@@ -5353,10 +4884,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5367,13 +4898,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="C8" s="3">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5381,7 +4912,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C9" s="3">
         <v>2.9</v>
@@ -5395,7 +4926,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C10" s="3">
         <v>2.6</v>
@@ -5409,7 +4940,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="C11" s="3">
         <v>2.4</v>
@@ -5423,7 +4954,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
@@ -5437,13 +4968,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5451,13 +4982,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.0</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5465,13 +4996,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5479,10 +5010,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C16" s="3">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -5505,15 +5036,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -5527,10 +5058,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
@@ -5538,10 +5069,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5560,7 +5091,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2">
@@ -5568,12 +5099,12 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -5589,7 +5120,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5597,7 +5128,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5605,7 +5136,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5613,7 +5144,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5621,7 +5152,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5648,10 +5179,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5663,10 +5194,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5683,31 +5214,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
@@ -5715,31 +5246,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
@@ -5747,31 +5278,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>215</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -5779,31 +5310,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="F5" s="3">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
@@ -5811,31 +5342,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F6" s="3">
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -5843,31 +5374,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F7" s="3">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8">
@@ -5875,31 +5406,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F8" s="3">
         <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5907,31 +5438,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="F9" s="3">
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>392</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -5939,31 +5470,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F10" s="3">
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -5971,31 +5502,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>298</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>370</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F11" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -6003,31 +5534,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>403</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -6035,31 +5566,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>404</v>
+        <v>347</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>407</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -6067,31 +5598,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>412</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -6099,31 +5630,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>120</v>
+        <v>384</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>121</v>
+        <v>385</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>83</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16">
@@ -6131,31 +5662,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>389</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>390</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F16" s="3">
         <v>56</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="F16" s="3">
-        <v>44</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>61</v>
+        <v>392</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
@@ -6163,31 +5694,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>393</v>
+        <v>209</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>147</v>
+        <v>264</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>166</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18">
@@ -6195,31 +5726,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19">
@@ -6227,31 +5758,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>242</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>428</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20">
@@ -6259,31 +5790,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>429</v>
+        <v>117</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -6291,31 +5822,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W30.xlsx
+++ b/reports/devops-jobs-israel-2026-W30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="436">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-24T08:38:01</t>
+    <t xml:space="preserve">2026-07-26T08:36:44</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7%</t>
+    <t xml:space="preserve">1.3%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -432,16 +432,61 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Infinity Solutions R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
+  </si>
+  <si>
     <t xml:space="preserve">AllCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
   </si>
   <si>
     <t xml:space="preserve">Echo</t>
@@ -453,12 +498,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
   </si>
   <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
@@ -468,9 +507,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4440107517</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops</t>
   </si>
   <si>
@@ -501,22 +537,307 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4442540495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4440126043</t>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps and Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mend.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-and-security-at-mend-io-4444431341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4445382643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-at-commit-4440117720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Automic Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-automic-platform-at-youcc-technologies-ltd-4441528264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer &amp; Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-tech-lead-at-mobileye-4366001366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4444432936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4443042028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-above-security-4443903986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
   </si>
   <si>
     <t xml:space="preserve">Nexxen</t>
@@ -528,130 +849,85 @@
     <t xml:space="preserve">2026-07-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-at-commit-4440117720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4441783259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4439678410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kms-lighthouse-4444830064</t>
   </si>
   <si>
     <t xml:space="preserve">Director of DevOps</t>
@@ -669,52 +945,109 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Director of QA Automation and DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinity Solutions R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4444973401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/engineering-manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudFormation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
@@ -723,312 +1056,15 @@
     <t xml:space="preserve">Helfy</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Automic Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-automic-platform-at-youcc-technologies-ltd-4441528264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4440112912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4443354508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-above-security-4443903986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QHR- ACCURATE HR SERVICES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-qhr-accurate-hr-services-4441512612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigation System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/navigation-system-engineer-at-iai-israel-aerospace-industries-4440139211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devsecops-engineer-at-confidential-4441781840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudFormation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
@@ -1047,9 +1083,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
   </si>
   <si>
@@ -1062,12 +1095,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
   </si>
   <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
   </si>
   <si>
@@ -1077,9 +1119,6 @@
     <t xml:space="preserve">MER Group</t>
   </si>
   <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1095,9 +1134,6 @@
     <t xml:space="preserve">Autobrains Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
   </si>
   <si>
@@ -1122,6 +1158,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -1131,15 +1176,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
   </si>
   <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4443827049</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -1149,15 +1185,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4442985724</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1188,18 +1215,6 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-cato-networks-4421931930</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
@@ -1227,37 +1242,34 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1275,13 +1287,16 @@
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1436,7 +1451,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -1444,7 +1459,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1452,7 +1467,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1460,7 +1475,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1081</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10">
@@ -1468,7 +1483,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1532,7 +1547,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -1559,36 +1574,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1596,7 +1611,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1615,39 +1630,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>414</v>
+        <v>321</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>416</v>
+        <v>325</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
@@ -1655,7 +1670,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -1663,7 +1678,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>314</v>
+        <v>421</v>
       </c>
       <c r="B7" s="3">
         <v>23</v>
@@ -1671,39 +1686,39 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B10" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="B11" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>308</v>
+        <v>424</v>
       </c>
       <c r="B12" s="3">
         <v>17</v>
@@ -1711,15 +1726,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>307</v>
+        <v>425</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1727,7 +1742,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>318</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -1735,10 +1750,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1763,13 +1778,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
@@ -1780,10 +1795,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>13.2</v>
+        <v>13.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1792,88 +1807,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3">
-        <v>38.2</v>
+        <v>36.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.7</v>
+        <v>29.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.9</v>
+        <v>15.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1884,7 +1899,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1957,7 +1972,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -1989,7 +2004,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -2021,7 +2036,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -2053,7 +2068,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -2085,7 +2100,7 @@
         <v>59</v>
       </c>
       <c r="J6" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2117,7 +2132,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -2149,7 +2164,7 @@
         <v>69</v>
       </c>
       <c r="J8" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -2181,7 +2196,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -2213,7 +2228,7 @@
         <v>69</v>
       </c>
       <c r="J10" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -2245,7 +2260,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -2277,7 +2292,7 @@
         <v>86</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -2309,7 +2324,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -2341,7 +2356,7 @@
         <v>73</v>
       </c>
       <c r="J14" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2373,7 +2388,7 @@
         <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -2405,7 +2420,7 @@
         <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -2437,7 +2452,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -2469,7 +2484,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -2501,7 +2516,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -2533,7 +2548,7 @@
         <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2563,7 +2578,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2595,7 +2610,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -2625,7 +2640,7 @@
         <v>132</v>
       </c>
       <c r="J23" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
@@ -2657,7 +2672,7 @@
         <v>73</v>
       </c>
       <c r="J24" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2671,7 +2686,7 @@
         <v>138</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>45</v>
@@ -2687,7 +2702,7 @@
         <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2701,7 +2716,7 @@
         <v>142</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>45</v>
@@ -2717,7 +2732,7 @@
         <v>140</v>
       </c>
       <c r="J26" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2728,7 +2743,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
@@ -2747,7 +2762,7 @@
         <v>140</v>
       </c>
       <c r="J27" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2758,7 +2773,7 @@
         <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2771,27 +2786,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2801,27 +2816,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J29" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2831,13 +2846,13 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J30" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2845,10 +2860,10 @@
         <v>106</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>44</v>
@@ -2861,10 +2876,10 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J31" s="3">
         <v>4</v>
@@ -2875,13 +2890,13 @@
         <v>106</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>45</v>
@@ -2891,27 +2906,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -2921,27 +2936,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J33" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>45</v>
@@ -2954,89 +2969,91 @@
         <v>170</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J34" s="3">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
@@ -3044,10 +3061,10 @@
         <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3058,37 +3075,39 @@
         <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
@@ -3101,84 +3120,84 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="J39" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
@@ -3191,43 +3210,43 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="J42" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44">
@@ -3238,7 +3257,7 @@
         <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
@@ -3254,57 +3273,57 @@
         <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="J45" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3314,54 +3333,54 @@
         <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="J46" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>142</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>38</v>
@@ -3371,24 +3390,24 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="J48" s="3">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>106</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
@@ -3401,13 +3420,13 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3415,13 +3434,13 @@
         <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>45</v>
@@ -3431,57 +3450,57 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>106</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>45</v>
@@ -3491,54 +3510,54 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J53" s="3">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>112</v>
@@ -3551,43 +3570,43 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3595,13 +3614,13 @@
         <v>106</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>45</v>
@@ -3611,57 +3630,59 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>245</v>
+        <v>178</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>45</v>
@@ -3674,24 +3695,24 @@
         <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>45</v>
@@ -3704,21 +3725,21 @@
         <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="J59" s="3">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>256</v>
+        <v>49</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>44</v>
@@ -3731,24 +3752,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>259</v>
+        <v>106</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>44</v>
@@ -3761,27 +3782,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J61" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>112</v>
+        <v>250</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>45</v>
@@ -3791,43 +3812,43 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -3835,13 +3856,13 @@
         <v>106</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>56</v>
+        <v>249</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>45</v>
@@ -3851,13 +3872,13 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -3865,10 +3886,10 @@
         <v>106</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>112</v>
@@ -3881,114 +3902,114 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>157</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="J66" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>176</v>
+        <v>275</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>112</v>
@@ -4001,27 +4022,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>45</v>
@@ -4031,54 +4052,54 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J70" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>286</v>
+        <v>186</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>112</v>
@@ -4091,30 +4112,30 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -4124,21 +4145,21 @@
         <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>112</v>
@@ -4151,42 +4172,40 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>300</v>
-      </c>
       <c r="I75" s="3" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="J75" s="3">
         <v>2</v>
@@ -4194,38 +4213,156 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J76" s="3">
-        <v>3</v>
+      <c r="I77" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J78" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J80" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J76"/>
+  <autoFilter ref="A1:J80"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4302,6 +4439,10 @@
     <hyperlink ref="H74" r:id="rId73"/>
     <hyperlink ref="H75" r:id="rId74"/>
     <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4309,9 +4450,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4343,13 +4484,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4357,18 +4498,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4376,18 +4517,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4395,18 +4536,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>212</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4414,18 +4555,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>275</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>186</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4433,18 +4574,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4452,18 +4593,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4471,18 +4612,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>295</v>
+        <v>138</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4490,11 +4631,30 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4504,6 +4664,7 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4517,15 +4678,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -4533,7 +4694,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3">
         <v>13</v>
@@ -4541,7 +4702,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B4" s="3">
         <v>12</v>
@@ -4549,7 +4710,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B5" s="3">
         <v>12</v>
@@ -4557,15 +4718,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
@@ -4573,7 +4734,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
@@ -4581,7 +4742,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B9" s="3">
         <v>7</v>
@@ -4589,7 +4750,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -4605,7 +4766,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
@@ -4613,7 +4774,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -4621,7 +4782,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -4629,7 +4790,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -4637,7 +4798,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -4659,7 +4820,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
@@ -4688,7 +4849,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -4696,15 +4857,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -4712,7 +4873,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -4720,7 +4881,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4728,7 +4889,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -4736,7 +4897,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -4744,15 +4905,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -4760,7 +4921,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -4768,7 +4929,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -4776,7 +4937,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -4797,16 +4958,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
@@ -4898,7 +5059,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C8" s="3">
         <v>3.6</v>
@@ -4912,13 +5073,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="C9" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4926,13 +5087,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4940,10 +5101,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="C11" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -4954,7 +5115,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
@@ -4968,13 +5129,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="C13" s="3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -4982,10 +5143,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3">
-        <v>2.0</v>
+        <v>2.3</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -4996,10 +5157,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3">
-        <v>1.4</v>
+        <v>2.0</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -5010,7 +5171,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3">
         <v>1.4</v>
@@ -5036,18 +5197,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5058,10 +5219,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -5069,10 +5230,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5091,7 +5252,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
@@ -5099,7 +5260,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -5107,7 +5268,7 @@
         <v>112</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -5120,18 +5281,18 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5144,7 +5305,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5152,7 +5313,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5179,10 +5340,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5194,10 +5355,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5214,31 +5375,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3">
@@ -5246,31 +5407,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>232</v>
+        <v>343</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>233</v>
+        <v>344</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>235</v>
+        <v>347</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -5278,31 +5439,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>342</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5">
@@ -5310,31 +5471,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
@@ -5342,31 +5503,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>348</v>
+        <v>186</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -5374,31 +5535,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="F7" s="3">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>355</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
@@ -5406,31 +5567,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -5438,31 +5599,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F9" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>245</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -5470,31 +5631,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="F10" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -5502,31 +5663,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>370</v>
+        <v>157</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>176</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12">
@@ -5534,31 +5695,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>382</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -5566,31 +5727,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>376</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>237</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F13" s="3">
         <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -5598,28 +5759,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F14" s="3">
         <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>80</v>
@@ -5630,31 +5791,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F15" s="3">
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16">
@@ -5662,31 +5823,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>390</v>
+        <v>206</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F16" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>176</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17">
@@ -5694,31 +5855,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>209</v>
+        <v>403</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18">
@@ -5726,31 +5887,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>398</v>
+        <v>117</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>401</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -5758,31 +5919,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>402</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>403</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>242</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>405</v>
+        <v>58</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>245</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -5790,31 +5951,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>356</v>
+        <v>410</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>260</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>80</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21">
@@ -5822,31 +5983,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F21" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>412</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
